--- a/Analysis/RAG_Ablation/rag_ablation_bootstrap_ci.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_bootstrap_ci.xlsx
@@ -460,13 +460,13 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.3256545778684238</v>
+        <v>0.2466139836730987</v>
       </c>
       <c r="D2" t="n">
-        <v>0.2075491240871846</v>
+        <v>0.1656649758247276</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4431605730722607</v>
+        <v>0.3240550350153702</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -486,13 +486,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>0.3159370989640887</v>
+        <v>0.2757061925995437</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2028985507246377</v>
+        <v>0.1939203993007504</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4262064969632444</v>
+        <v>0.3561293710362565</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -512,13 +512,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.1087540930495027</v>
+        <v>0.06831302849881668</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.007906274145351338</v>
+        <v>-0.01052352540342323</v>
       </c>
       <c r="E4" t="n">
-        <v>0.2191169040536979</v>
+        <v>0.1493017670003281</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -538,13 +538,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>0.299872137990063</v>
+        <v>0.2790198469760696</v>
       </c>
       <c r="D5" t="n">
-        <v>0.1814958217764944</v>
+        <v>0.1994949231688788</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4131337201244105</v>
+        <v>0.3591736250297444</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -564,13 +564,13 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.03888078956798695</v>
+        <v>0.001122450160373826</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3333333333333333</v>
+        <v>-0.1752869191630169</v>
       </c>
       <c r="E6" t="n">
-        <v>0.2611030117902092</v>
+        <v>0.1722222222222222</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
@@ -590,13 +590,13 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>0.06167510761155603</v>
+        <v>0.1206276471516558</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.05839416058394162</v>
+        <v>0.04415222706218069</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1826072844352711</v>
+        <v>0.1961007731794875</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
@@ -616,13 +616,13 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>0.3636485755005238</v>
+        <v>0.241260146786492</v>
       </c>
       <c r="D8" t="n">
-        <v>0.2495243032446883</v>
+        <v>0.159599533802982</v>
       </c>
       <c r="E8" t="n">
-        <v>0.4736828048778277</v>
+        <v>0.3254007973421639</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
@@ -642,13 +642,13 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>0.3877624423422041</v>
+        <v>0.2295533300979016</v>
       </c>
       <c r="D9" t="n">
-        <v>0.2849933608250722</v>
+        <v>0.1464059644292729</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4860837852678635</v>
+        <v>0.3107489404843378</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
@@ -668,13 +668,13 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>0.08066666666666666</v>
+        <v>0.1014228395061728</v>
       </c>
       <c r="D10" t="n">
-        <v>0.0702577380952381</v>
+        <v>0.09277552469135802</v>
       </c>
       <c r="E10" t="n">
-        <v>0.09170973214285714</v>
+        <v>0.1105248611111111</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
@@ -694,13 +694,13 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>0.08592380952380953</v>
+        <v>0.09829999999999998</v>
       </c>
       <c r="D11" t="n">
-        <v>0.07349270833333334</v>
+        <v>0.08994134259259258</v>
       </c>
       <c r="E11" t="n">
-        <v>0.09906913690476192</v>
+        <v>0.1071938888888889</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
@@ -720,13 +720,13 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>0.1418053571428571</v>
+        <v>0.146637037037037</v>
       </c>
       <c r="D12" t="n">
-        <v>0.1262938541666667</v>
+        <v>0.1361506172839506</v>
       </c>
       <c r="E12" t="n">
-        <v>0.1579161011904762</v>
+        <v>0.157760524691358</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
@@ -746,13 +746,13 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.08537619047619047</v>
+        <v>0.09734999999999999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.07348071428571427</v>
+        <v>0.0892596450617284</v>
       </c>
       <c r="E13" t="n">
-        <v>0.09776339285714283</v>
+        <v>0.1056606790123457</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
@@ -772,13 +772,13 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>0.09595132275132275</v>
+        <v>0.1009487654320988</v>
       </c>
       <c r="D14" t="n">
-        <v>0.07542733465608467</v>
+        <v>0.08767002829218108</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1178050066137566</v>
+        <v>0.1152905606995884</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
@@ -798,13 +798,13 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>0.1518154761904762</v>
+        <v>0.1436111111111111</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1338416071428571</v>
+        <v>0.1328731172839506</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1701109523809524</v>
+        <v>0.1547836882716049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
@@ -824,13 +824,13 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>0.09274880952380953</v>
+        <v>0.1043944444444444</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0804416369047619</v>
+        <v>0.09579194444444444</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1056786011904762</v>
+        <v>0.1134031327160494</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
@@ -850,13 +850,13 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>0.07858214285714286</v>
+        <v>0.09127777777777776</v>
       </c>
       <c r="D17" t="n">
-        <v>0.06787464285714284</v>
+        <v>0.08379691358024691</v>
       </c>
       <c r="E17" t="n">
-        <v>0.08991333333333335</v>
+        <v>0.0990798611111111</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -876,13 +876,13 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>0.5642857142857143</v>
+        <v>0.4703703703703704</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4785714285714286</v>
+        <v>0.4111111111111111</v>
       </c>
       <c r="E18" t="n">
-        <v>0.6428571428571429</v>
+        <v>0.5296296296296297</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
@@ -902,13 +902,13 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>0.5785714285714286</v>
+        <v>0.5037037037037037</v>
       </c>
       <c r="D19" t="n">
-        <v>0.5</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="E19" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.562962962962963</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
@@ -928,13 +928,13 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>0.4214285714285714</v>
+        <v>0.3888888888888889</v>
       </c>
       <c r="D20" t="n">
-        <v>0.3428571428571429</v>
+        <v>0.3296296296296296</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5071428571428571</v>
+        <v>0.4481481481481481</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
@@ -954,13 +954,13 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>0.5428571428571428</v>
+        <v>0.5</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.4407407407407408</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5592592592592592</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
@@ -980,13 +980,13 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>0.4571428571428571</v>
+        <v>0.4444444444444444</v>
       </c>
       <c r="D22" t="n">
-        <v>0.2857142857142857</v>
+        <v>0.3444444444444444</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6285714285714286</v>
+        <v>0.5444444444444444</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
@@ -1006,13 +1006,13 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>0.4071428571428571</v>
+        <v>0.4370370370370371</v>
       </c>
       <c r="D23" t="n">
-        <v>0.3285714285714286</v>
+        <v>0.3777777777777778</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4928571428571429</v>
+        <v>0.4962962962962963</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
@@ -1032,13 +1032,13 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>0.5857142857142857</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="D24" t="n">
-        <v>0.5</v>
+        <v>0.4296296296296296</v>
       </c>
       <c r="E24" t="n">
-        <v>0.6714285714285714</v>
+        <v>0.5481481481481482</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1058,13 +1058,13 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>0.55</v>
+        <v>0.4666666666666667</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="E25" t="n">
-        <v>0.6357142857142857</v>
+        <v>0.5259259259259259</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>

--- a/Analysis/RAG_Ablation/rag_ablation_bootstrap_ci.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_bootstrap_ci.xlsx
@@ -512,7 +512,7 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>0.06831302849881668</v>
+        <v>0.06831302849881667</v>
       </c>
       <c r="D4" t="n">
         <v>-0.01052352540342323</v>
@@ -564,7 +564,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>0.001122450160373826</v>
+        <v>0.001122450160373833</v>
       </c>
       <c r="D6" t="n">
         <v>-0.1752869191630169</v>
@@ -593,7 +593,7 @@
         <v>0.1206276471516558</v>
       </c>
       <c r="D7" t="n">
-        <v>0.04415222706218069</v>
+        <v>0.0441522270621807</v>
       </c>
       <c r="E7" t="n">
         <v>0.1961007731794875</v>
@@ -671,7 +671,7 @@
         <v>0.1014228395061728</v>
       </c>
       <c r="D10" t="n">
-        <v>0.09277552469135802</v>
+        <v>0.09277552469135801</v>
       </c>
       <c r="E10" t="n">
         <v>0.1105248611111111</v>
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>0.09734999999999999</v>
+        <v>0.09735000000000001</v>
       </c>
       <c r="D13" t="n">
         <v>0.0892596450617284</v>

--- a/Analysis/RAG_Ablation/rag_ablation_bootstrap_ci.xlsx
+++ b/Analysis/RAG_Ablation/rag_ablation_bootstrap_ci.xlsx
@@ -413,36 +413,41 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F25"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>model_key</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>ablation_id</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>ablation_label</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>point_estimate</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="E1" t="inlineStr">
         <is>
           <t>ci_lower</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="F1" t="inlineStr">
         <is>
           <t>ci_upper</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="G1" t="inlineStr">
         <is>
           <t>metric</t>
         </is>
@@ -451,24 +456,29 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
           <t>alternate_embedding_k3</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
+      <c r="C2" t="inlineStr">
         <is>
           <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
         </is>
       </c>
-      <c r="C2" t="n">
-        <v>0.2466139836730987</v>
-      </c>
       <c r="D2" t="n">
-        <v>0.1656649758247276</v>
+        <v>0.3462527705722217</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3240550350153702</v>
-      </c>
-      <c r="F2" t="inlineStr">
+        <v>0.2185335926155414</v>
+      </c>
+      <c r="F2" t="n">
+        <v>0.4752770767249676</v>
+      </c>
+      <c r="G2" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -477,24 +487,29 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
           <t>control_k3</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="C3" t="inlineStr">
         <is>
           <t>Control k=3 standard</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>0.2757061925995437</v>
-      </c>
       <c r="D3" t="n">
-        <v>0.1939203993007504</v>
+        <v>0.4887449341866358</v>
       </c>
       <c r="E3" t="n">
-        <v>0.3561293710362565</v>
-      </c>
-      <c r="F3" t="inlineStr">
+        <v>0.3666576373214672</v>
+      </c>
+      <c r="F3" t="n">
+        <v>0.6082167674659106</v>
+      </c>
+      <c r="G3" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -503,24 +518,29 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
           <t>descriptions_no_scores_ranks</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Descriptions without scores or ranks</t>
         </is>
       </c>
-      <c r="C4" t="n">
-        <v>0.06831302849881667</v>
-      </c>
       <c r="D4" t="n">
-        <v>-0.01052352540342323</v>
+        <v>0.07325185847118744</v>
       </c>
       <c r="E4" t="n">
-        <v>0.1493017670003281</v>
-      </c>
-      <c r="F4" t="inlineStr">
+        <v>-0.05949019080755633</v>
+      </c>
+      <c r="F4" t="n">
+        <v>0.20425169944457</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -529,24 +549,29 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
+          <t>deepseek</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
           <t>exemplars_no_hidden_params</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
+      <c r="C5" t="inlineStr">
         <is>
           <t>Exemplars without hidden parameters</t>
         </is>
       </c>
-      <c r="C5" t="n">
-        <v>0.2790198469760696</v>
-      </c>
       <c r="D5" t="n">
-        <v>0.1994949231688788</v>
+        <v>0.391088820886045</v>
       </c>
       <c r="E5" t="n">
-        <v>0.3591736250297444</v>
-      </c>
-      <c r="F5" t="inlineStr">
+        <v>0.2554904914499362</v>
+      </c>
+      <c r="F5" t="n">
+        <v>0.5208140054084537</v>
+      </c>
+      <c r="G5" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -555,24 +580,29 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
-        </is>
-      </c>
-      <c r="C6" t="n">
-        <v>0.001122450160373833</v>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
       </c>
       <c r="D6" t="n">
-        <v>-0.1752869191630169</v>
+        <v>0.06319016102054624</v>
       </c>
       <c r="E6" t="n">
-        <v>0.1722222222222222</v>
-      </c>
-      <c r="F6" t="inlineStr">
+        <v>-0.07652072147964215</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0.2042570882846266</v>
+      </c>
+      <c r="G6" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -581,24 +611,29 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="C7" t="n">
-        <v>0.1206276471516558</v>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
       </c>
       <c r="D7" t="n">
-        <v>0.0441522270621807</v>
+        <v>0.1822297815883974</v>
       </c>
       <c r="E7" t="n">
-        <v>0.1961007731794875</v>
-      </c>
-      <c r="F7" t="inlineStr">
+        <v>0.03724301047920384</v>
+      </c>
+      <c r="F7" t="n">
+        <v>0.3181443684650606</v>
+      </c>
+      <c r="G7" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -607,24 +642,29 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="C8" t="n">
-        <v>0.241260146786492</v>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
       </c>
       <c r="D8" t="n">
-        <v>0.159599533802982</v>
+        <v>0.3421290982335188</v>
       </c>
       <c r="E8" t="n">
-        <v>0.3254007973421639</v>
-      </c>
-      <c r="F8" t="inlineStr">
+        <v>0.2022471910112359</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0.4745203687516819</v>
+      </c>
+      <c r="G8" t="inlineStr">
         <is>
           <t>kendall_tau</t>
         </is>
@@ -633,50 +673,60 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
-        </is>
-      </c>
-      <c r="C9" t="n">
-        <v>0.2295533300979016</v>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
       </c>
       <c r="D9" t="n">
-        <v>0.1464059644292729</v>
+        <v>0.08762962962962963</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3107489404843378</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>kendall_tau</t>
+        <v>0.07522384259259259</v>
+      </c>
+      <c r="F9" t="n">
+        <v>0.100665</v>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>score_mae</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
-        </is>
-      </c>
-      <c r="C10" t="n">
-        <v>0.1014228395061728</v>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
       </c>
       <c r="D10" t="n">
-        <v>0.09277552469135801</v>
+        <v>0.08843888888888889</v>
       </c>
       <c r="E10" t="n">
-        <v>0.1105248611111111</v>
-      </c>
-      <c r="F10" t="inlineStr">
+        <v>0.07407592592592592</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0.1043752314814814</v>
+      </c>
+      <c r="G10" t="inlineStr">
         <is>
           <t>score_mae</t>
         </is>
@@ -685,24 +735,29 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
-        </is>
-      </c>
-      <c r="C11" t="n">
-        <v>0.09829999999999998</v>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
       </c>
       <c r="D11" t="n">
-        <v>0.08994134259259258</v>
+        <v>0.131162962962963</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1071938888888889</v>
-      </c>
-      <c r="F11" t="inlineStr">
+        <v>0.1164332870370371</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.1465317592592593</v>
+      </c>
+      <c r="G11" t="inlineStr">
         <is>
           <t>score_mae</t>
         </is>
@@ -711,24 +766,29 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
-        </is>
-      </c>
-      <c r="C12" t="n">
-        <v>0.146637037037037</v>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
       </c>
       <c r="D12" t="n">
-        <v>0.1361506172839506</v>
+        <v>0.08744999999999997</v>
       </c>
       <c r="E12" t="n">
-        <v>0.157760524691358</v>
-      </c>
-      <c r="F12" t="inlineStr">
+        <v>0.07401851851851853</v>
+      </c>
+      <c r="F12" t="n">
+        <v>0.1021560185185185</v>
+      </c>
+      <c r="G12" t="inlineStr">
         <is>
           <t>score_mae</t>
         </is>
@@ -737,24 +797,29 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
-        </is>
-      </c>
-      <c r="C13" t="n">
-        <v>0.09735000000000001</v>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
       </c>
       <c r="D13" t="n">
-        <v>0.0892596450617284</v>
+        <v>0.1267</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1056606790123457</v>
-      </c>
-      <c r="F13" t="inlineStr">
+        <v>0.1125271759259259</v>
+      </c>
+      <c r="F13" t="n">
+        <v>0.1413913425925926</v>
+      </c>
+      <c r="G13" t="inlineStr">
         <is>
           <t>score_mae</t>
         </is>
@@ -763,24 +828,29 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
-        </is>
-      </c>
-      <c r="C14" t="n">
-        <v>0.1009487654320988</v>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
       </c>
       <c r="D14" t="n">
-        <v>0.08767002829218108</v>
+        <v>0.09810925925925926</v>
       </c>
       <c r="E14" t="n">
-        <v>0.1152905606995884</v>
-      </c>
-      <c r="F14" t="inlineStr">
+        <v>0.08503319444444443</v>
+      </c>
+      <c r="F14" t="n">
+        <v>0.1115593518518519</v>
+      </c>
+      <c r="G14" t="inlineStr">
         <is>
           <t>score_mae</t>
         </is>
@@ -789,24 +859,29 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="C15" t="n">
-        <v>0.1436111111111111</v>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
       </c>
       <c r="D15" t="n">
-        <v>0.1328731172839506</v>
+        <v>0.08424629629629629</v>
       </c>
       <c r="E15" t="n">
-        <v>0.1547836882716049</v>
-      </c>
-      <c r="F15" t="inlineStr">
+        <v>0.07188249999999996</v>
+      </c>
+      <c r="F15" t="n">
+        <v>0.09726370370370369</v>
+      </c>
+      <c r="G15" t="inlineStr">
         <is>
           <t>score_mae</t>
         </is>
@@ -815,76 +890,91 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="C16" t="n">
-        <v>0.1043944444444444</v>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
       </c>
       <c r="D16" t="n">
-        <v>0.09579194444444444</v>
+        <v>0.4888888888888889</v>
       </c>
       <c r="E16" t="n">
-        <v>0.1134031327160494</v>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>score_mae</t>
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F16" t="n">
+        <v>0.5888888888888889</v>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>retrieval_k5</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Retrieval k=5</t>
-        </is>
-      </c>
-      <c r="C17" t="n">
-        <v>0.09127777777777776</v>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
       </c>
       <c r="D17" t="n">
-        <v>0.08379691358024691</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="E17" t="n">
-        <v>0.0990798611111111</v>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>score_mae</t>
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="F17" t="n">
+        <v>0.7333333333333333</v>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>alternate_embedding_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
-        </is>
-      </c>
-      <c r="C18" t="n">
-        <v>0.4703703703703704</v>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
       </c>
       <c r="D18" t="n">
         <v>0.4111111111111111</v>
       </c>
       <c r="E18" t="n">
-        <v>0.5296296296296297</v>
-      </c>
-      <c r="F18" t="inlineStr">
+        <v>0.3111111111111111</v>
+      </c>
+      <c r="F18" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="G18" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
@@ -893,24 +983,29 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>control_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Control k=3 standard</t>
-        </is>
-      </c>
-      <c r="C19" t="n">
-        <v>0.5037037037037037</v>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
       </c>
       <c r="D19" t="n">
-        <v>0.4444444444444444</v>
+        <v>0.5888888888888889</v>
       </c>
       <c r="E19" t="n">
-        <v>0.562962962962963</v>
-      </c>
-      <c r="F19" t="inlineStr">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="F19" t="n">
+        <v>0.6888888888888889</v>
+      </c>
+      <c r="G19" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
@@ -919,24 +1014,29 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>descriptions_no_scores_ranks</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Descriptions without scores or ranks</t>
-        </is>
-      </c>
-      <c r="C20" t="n">
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
         <v>0.3888888888888889</v>
       </c>
-      <c r="D20" t="n">
-        <v>0.3296296296296296</v>
-      </c>
       <c r="E20" t="n">
-        <v>0.4481481481481481</v>
-      </c>
-      <c r="F20" t="inlineStr">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="F20" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="G20" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
@@ -945,24 +1045,29 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>exemplars_no_hidden_params</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Exemplars without hidden parameters</t>
-        </is>
-      </c>
-      <c r="C21" t="n">
-        <v>0.5</v>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
       </c>
       <c r="D21" t="n">
-        <v>0.4407407407407408</v>
+        <v>0.4777777777777778</v>
       </c>
       <c r="E21" t="n">
-        <v>0.5592592592592592</v>
-      </c>
-      <c r="F21" t="inlineStr">
+        <v>0.3777777777777778</v>
+      </c>
+      <c r="F21" t="n">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="G21" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
@@ -971,24 +1076,29 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>nearest_neighbor_k3</t>
+          <t>deepseek</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Nearest-neighbor prediction k=3</t>
-        </is>
-      </c>
-      <c r="C22" t="n">
-        <v>0.4444444444444444</v>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
       </c>
       <c r="D22" t="n">
-        <v>0.3444444444444444</v>
+        <v>0.5222222222222223</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5444444444444444</v>
-      </c>
-      <c r="F22" t="inlineStr">
+        <v>0.4222222222222222</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.6222222222222222</v>
+      </c>
+      <c r="G22" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
@@ -997,76 +1107,2044 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>random_exemplars_k3</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Random exemplars k=3</t>
-        </is>
-      </c>
-      <c r="C23" t="n">
-        <v>0.4370370370370371</v>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
       </c>
       <c r="D23" t="n">
-        <v>0.3777777777777778</v>
+        <v>0.5173960683581447</v>
       </c>
       <c r="E23" t="n">
-        <v>0.4962962962962963</v>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
+        <v>0.3823979581996885</v>
+      </c>
+      <c r="F23" t="n">
+        <v>0.6449867711091934</v>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>retrieval_k1</t>
+          <t>gemini</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Retrieval k=1</t>
-        </is>
-      </c>
-      <c r="C24" t="n">
-        <v>0.4888888888888889</v>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
       </c>
       <c r="D24" t="n">
-        <v>0.4296296296296296</v>
+        <v>0.3868499620103081</v>
       </c>
       <c r="E24" t="n">
-        <v>0.5481481481481482</v>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>top1_accuracy</t>
+        <v>0.2399924406338249</v>
+      </c>
+      <c r="F24" t="n">
+        <v>0.5296389833809658</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>0.2037037037037037</v>
+      </c>
+      <c r="E25" t="n">
+        <v>0.06870559354524748</v>
+      </c>
+      <c r="F25" t="n">
+        <v>0.3366628869835791</v>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>0.4366628869835791</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0.2992423461417477</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0.56387943968117</v>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>0.1774036277243198</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.04331778986878833</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0.313692364654441</v>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>0.3774036277243198</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0.2379441600039076</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0.513318214600983</v>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
           <t>retrieval_k5</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C29" t="inlineStr">
         <is>
           <t>Retrieval k=5</t>
         </is>
       </c>
-      <c r="C25" t="n">
+      <c r="D29" t="n">
+        <v>0.4312944064547524</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0.2990741695304566</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0.5609240360843821</v>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>0.07113148148148148</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0.0592610648148148</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0.08417791666666667</v>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>0.07047777777777779</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0.05944962962962963</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0.08271675925925927</v>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1426777777777778</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0.1246351851851852</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0.1612778703703704</v>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D33" t="n">
+        <v>0.0779425925925926</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0.06481657407407408</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0.09227439814814815</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1391074074074074</v>
+      </c>
+      <c r="E34" t="n">
+        <v>0.1208490277777778</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0.1583835185185185</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D35" t="n">
+        <v>0.09680925925925926</v>
+      </c>
+      <c r="E35" t="n">
+        <v>0.08117032407407407</v>
+      </c>
+      <c r="F35" t="n">
+        <v>0.1142503703703703</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D36" t="n">
+        <v>0.06913888888888887</v>
+      </c>
+      <c r="E36" t="n">
+        <v>0.05774060185185185</v>
+      </c>
+      <c r="F36" t="n">
+        <v>0.08147407407407406</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D37" t="n">
+        <v>0.7222222222222222</v>
+      </c>
+      <c r="E37" t="n">
+        <v>0.6333333333333333</v>
+      </c>
+      <c r="F37" t="n">
+        <v>0.8111111111111111</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D38" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="E38" t="n">
         <v>0.4666666666666667</v>
       </c>
-      <c r="D25" t="n">
-        <v>0.4074074074074074</v>
-      </c>
-      <c r="E25" t="n">
-        <v>0.5259259259259259</v>
-      </c>
-      <c r="F25" t="inlineStr">
+      <c r="F38" t="n">
+        <v>0.6666666666666666</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D39" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="E39" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="F39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D40" t="n">
+        <v>0.6111111111111112</v>
+      </c>
+      <c r="E40" t="n">
+        <v>0.5111111111111111</v>
+      </c>
+      <c r="F40" t="n">
+        <v>0.7111111111111111</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D41" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="E41" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F41" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D42" t="n">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="E42" t="n">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="F42" t="n">
+        <v>0.6777777777777778</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>gemini</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D43" t="n">
+        <v>0.6444444444444445</v>
+      </c>
+      <c r="E43" t="n">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="F43" t="n">
+        <v>0.7444444444444445</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D44" t="n">
+        <v>0.226842402644133</v>
+      </c>
+      <c r="E44" t="n">
+        <v>0.09425736941771547</v>
+      </c>
+      <c r="F44" t="n">
+        <v>0.3601757359774662</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D45" t="n">
+        <v>0.187224112063766</v>
+      </c>
+      <c r="E45" t="n">
+        <v>0.04444444444444443</v>
+      </c>
+      <c r="F45" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D46" t="n">
+        <v>0.06092403608438215</v>
+      </c>
+      <c r="E46" t="n">
+        <v>-0.07536470084573901</v>
+      </c>
+      <c r="F46" t="n">
+        <v>0.1951738461359225</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D47" t="n">
+        <v>0.175364700845739</v>
+      </c>
+      <c r="E47" t="n">
+        <v>0.02721655269759088</v>
+      </c>
+      <c r="F47" t="n">
+        <v>0.3198091452901835</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D48" t="n">
+        <v>0.02222222222222222</v>
+      </c>
+      <c r="E48" t="n">
+        <v>-0.1074074074074074</v>
+      </c>
+      <c r="F48" t="n">
+        <v>0.1494387749198131</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D49" t="n">
+        <v>0.2366628869835791</v>
+      </c>
+      <c r="E49" t="n">
+        <v>0.0975733649013425</v>
+      </c>
+      <c r="F49" t="n">
+        <v>0.3729516239137002</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D50" t="n">
+        <v>0.1123595505617977</v>
+      </c>
+      <c r="E50" t="n">
+        <v>-0.03370786516853932</v>
+      </c>
+      <c r="F50" t="n">
+        <v>0.2638557668269033</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D51" t="n">
+        <v>0.1127148148148148</v>
+      </c>
+      <c r="E51" t="n">
+        <v>0.09612537037037039</v>
+      </c>
+      <c r="F51" t="n">
+        <v>0.1301574074074074</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D52" t="n">
+        <v>0.1045222222222222</v>
+      </c>
+      <c r="E52" t="n">
+        <v>0.08988291666666666</v>
+      </c>
+      <c r="F52" t="n">
+        <v>0.1203445370370371</v>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D53" t="n">
+        <v>0.157687037037037</v>
+      </c>
+      <c r="E53" t="n">
+        <v>0.1382676851851852</v>
+      </c>
+      <c r="F53" t="n">
+        <v>0.1773247685185185</v>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D54" t="n">
+        <v>0.1058314814814815</v>
+      </c>
+      <c r="E54" t="n">
+        <v>0.09129175925925925</v>
+      </c>
+      <c r="F54" t="n">
+        <v>0.1211613888888889</v>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D55" t="n">
+        <v>0.1634185185185185</v>
+      </c>
+      <c r="E55" t="n">
+        <v>0.1418477777777778</v>
+      </c>
+      <c r="F55" t="n">
+        <v>0.1852059722222222</v>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>0.1182425925925926</v>
+      </c>
+      <c r="E56" t="n">
+        <v>0.1012887962962963</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0.1355209722222222</v>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>0.1016333333333333</v>
+      </c>
+      <c r="E57" t="n">
+        <v>0.08702930555555555</v>
+      </c>
+      <c r="F57" t="n">
+        <v>0.117042037037037</v>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="E58" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="F58" t="n">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="F59" t="n">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="E60" t="n">
+        <v>0.2333333333333333</v>
+      </c>
+      <c r="F60" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="E61" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="F61" t="n">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="E62" t="n">
+        <v>0.2444444444444444</v>
+      </c>
+      <c r="F62" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="E63" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="F63" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>gptoss</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="E64" t="n">
+        <v>0.2888888888888889</v>
+      </c>
+      <c r="F64" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>nearest_neighbor_k3</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Nearest-neighbor prediction k=3</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>0.001122450160373833</v>
+      </c>
+      <c r="E65" t="n">
+        <v>-0.1724744871391589</v>
+      </c>
+      <c r="F65" t="n">
+        <v>0.1752806125400935</v>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>nearest_neighbor_k3</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Nearest-neighbor prediction k=3</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>0.1009487654320988</v>
+      </c>
+      <c r="E66" t="n">
+        <v>0.08783149691358022</v>
+      </c>
+      <c r="F66" t="n">
+        <v>0.1153469830246914</v>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>offline</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>nearest_neighbor_k3</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Nearest-neighbor prediction k=3</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>0.4444444444444444</v>
+      </c>
+      <c r="E67" t="n">
+        <v>0.3444444444444444</v>
+      </c>
+      <c r="F67" t="n">
+        <v>0.5444444444444444</v>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>0.1651380096338454</v>
+      </c>
+      <c r="E68" t="n">
+        <v>0.01475496661937513</v>
+      </c>
+      <c r="F68" t="n">
+        <v>0.3170639328667061</v>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>0.1535166286769747</v>
+      </c>
+      <c r="E69" t="n">
+        <v>0.009811130588109715</v>
+      </c>
+      <c r="F69" t="n">
+        <v>0.2959221462428384</v>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>0.07107475194335945</v>
+      </c>
+      <c r="E70" t="n">
+        <v>-0.06897954293098491</v>
+      </c>
+      <c r="F70" t="n">
+        <v>0.2128372040506391</v>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>0.2730298857137317</v>
+      </c>
+      <c r="E71" t="n">
+        <v>0.1368932968435087</v>
+      </c>
+      <c r="F71" t="n">
+        <v>0.4067262844279604</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>0.275640142105863</v>
+      </c>
+      <c r="E72" t="n">
+        <v>0.1490560261091113</v>
+      </c>
+      <c r="F72" t="n">
+        <v>0.3981005857639119</v>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>0.3056026889223424</v>
+      </c>
+      <c r="E73" t="n">
+        <v>0.1644156535039938</v>
+      </c>
+      <c r="F73" t="n">
+        <v>0.4434227599752739</v>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>0.2342775026800086</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.1026644960087045</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0.3616623636528664</v>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>kendall_tau</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>0.1039240740740741</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.08938287037037038</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0.119716712962963</v>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>0.1019388888888889</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.08684620370370369</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0.1171061111111111</v>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>0.1510611111111111</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.1311275925925926</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0.1721578240740741</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>0.09876851851851849</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.08505171296296295</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0.1131778240740741</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>0.1407148148148148</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.1220073611111111</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0.1605870833333333</v>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>0.09683148148148148</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.08380351851851851</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.1108928703703704</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>0.08795370370370369</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.07613504629629629</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0.1002687962962963</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>score_mae</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>alternate_embedding_k3</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Alternate embedding k=3 (sentence-transformers/paraphrase-MiniLM-L3-v2)</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.3777777777777778</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>control_k3</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Control k=3 standard</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>0.4333333333333333</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.3333333333333333</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0.5333333333333333</v>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>descriptions_no_scores_ranks</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Descriptions without scores or ranks</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>0.4222222222222222</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.3222222222222222</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.5222222222222223</v>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>exemplars_no_hidden_params</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Exemplars without hidden parameters</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>0.4666666666666667</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.3666666666666666</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.5666666666666667</v>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>random_exemplars_k3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Random exemplars k=3</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>0.5777777777777777</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.4777777777777778</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.6777777777777778</v>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>retrieval_k1</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Retrieval k=1</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>0.5222222222222223</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.4222222222222222</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.6222222222222222</v>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>top1_accuracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>qwen</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>retrieval_k5</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Retrieval k=5</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>0.4888888888888889</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.3888888888888889</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.5888888888888889</v>
+      </c>
+      <c r="G88" t="inlineStr">
         <is>
           <t>top1_accuracy</t>
         </is>
